--- a/Performance_Test_Report.xlsx
+++ b/Performance_Test_Report.xlsx
@@ -7,9 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Performance_Test_Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Performance Metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Configuration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metric Definitions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Performance Metrics'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Configuration'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Metric Definitions'!$A$1:$B$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +31,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +140,145 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Average Response Time by Scenario</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Performance Metrics'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Performance Metrics'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Performance Metrics'!$C$2:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Scenario</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Milliseconds</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,472 +570,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>feature</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>automation</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>source</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Requests/sec</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Avg response (ms)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Min response (ms)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Max response (ms)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Throughput (req)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Error rate (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Success rate (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-091</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Verify dashboard load behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>dashboard load</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pending execution</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-092</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Verify patient list render behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>patient list render</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pending execution</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-093</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Verify report search response behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>report search response</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pending execution</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC-094</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Verify image preprocessing behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>image preprocessing</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
+          <t>Add Patient</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pending execution</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC-095</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Verify large patient dataset behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>large patient dataset</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
+          <t>Patient List</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pending execution</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC-096</t>
+          <t>Image Upload / Diagnosis</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pending execution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>k6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Load model</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>constant-vus</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Virtual users</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Duration per scenario</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1 minute</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BASE_URL or http://127.0.0.1:5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data policy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verify repeated login attempts behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>repeated login attempts</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
+          <t>Synthetic accounts and patient data only</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC-097</t>
+          <t>Execution status</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verify concurrent uploads behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>concurrent uploads</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TC-098</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Verify report export handling behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>report export handling</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TC-099</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Verify route rendering under load behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>route rendering under load</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TC-100</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Verify image save performance behaves correctly for the performance testing scenario</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Performance Testing</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>image save performance</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Repository feature mapping</t>
+          <t>Template - not executed</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source / interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Requests/sec</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>k6 http_reqs rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Average / min / max response time</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>k6 http_req_duration values</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Throughput</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Completed HTTP requests in the scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Error rate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>k6 http_req_failed rate multiplied by 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Success rate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Scenario-specific custom success Rate multiplied by 100</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>